--- a/samples/ss_ungaran12_ingest.xlsx
+++ b/samples/ss_ungaran12_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_ungaran12_ingest.xlsx
+++ b/samples/ss_ungaran12_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Ungaran 500/150 kV</t>
+          <t>IBT 1 Ungaran 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ungaran (bus 150 kV)</t>
+          <t>IBT 2 Ungaran 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 UNGAR7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UNGAR7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>UNGAR</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1;2</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -791,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jelok</t>
+          <t>Ungaran (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JELOK</t>
+          <t>UNGAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -844,17 +858,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTA Jelok</t>
+          <t>Jelok</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_JELOK</t>
+          <t>JELOK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -897,12 +911,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLTA Timo</t>
+          <t>PLTA Jelok</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_TIMO</t>
+          <t>KIT_JELOK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,17 +964,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tambaklorok</t>
+          <t>PLTA Timo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TBROK</t>
+          <t>KIT_TIMO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -986,14 +1000,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1007,17 +1017,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTGU Tambaklorok Blok B3</t>
+          <t>Tambaklorok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_TBROKB3</t>
+          <t>TBROK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1048,7 +1058,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1064,12 +1074,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PLTGU Tambaklorok Blok B1</t>
+          <t>PLTGU Tambaklorok Blok B3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KIT_TBROKB1</t>
+          <t>KIT_TBROKB3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1100,10 +1110,14 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1117,21 +1131,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weleri</t>
+          <t>PLTGU Tambaklorok Blok B1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WLERI</t>
+          <t>KIT_TBROKB1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1153,14 +1167,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1174,12 +1184,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Payung</t>
+          <t>Weleri</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PYUNG</t>
+          <t>WLERI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1215,7 +1225,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1231,12 +1241,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Krapyak</t>
+          <t>Payung</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KRAPK</t>
+          <t>PYUNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1272,7 +1282,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1288,12 +1298,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pandean Lamper</t>
+          <t>Krapyak</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PDLAM</t>
+          <t>KRAPK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1324,10 +1334,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1341,12 +1355,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kalisari</t>
+          <t>Pandean Lamper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KLSRI</t>
+          <t>PDLAM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1377,14 +1391,10 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1398,12 +1408,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sayung</t>
+          <t>Kalisari</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SYUNG</t>
+          <t>KLSRI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1439,7 +1449,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1455,12 +1465,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kaliwungu</t>
+          <t>Sayung</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KLNGU</t>
+          <t>SYUNG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1469,7 +1479,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1481,11 +1491,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>KTT APF</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1500,7 +1506,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1516,12 +1522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bawen Sambiroto Baru</t>
+          <t>Kaliwungu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BSBRU</t>
+          <t>KLNGU</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1542,7 +1548,11 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>KTT APF</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
@@ -1552,10 +1562,14 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1569,12 +1583,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Randu Garut</t>
+          <t>Bawen Sambiroto Baru</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RDRUT</t>
+          <t>BSBRU</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1605,14 +1619,10 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1626,12 +1636,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Srondol</t>
+          <t>Randu Garut</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SRDOL</t>
+          <t>RDRUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1667,7 +1677,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1683,12 +1693,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selima (rencana)</t>
+          <t>Srondol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLIMA</t>
+          <t>SRDOL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1713,7 +1723,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1724,7 +1734,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6;7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1740,12 +1750,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Banaran / Sugihrahayu (SS Boyolali)</t>
+          <t>Selima</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRNGI</t>
+          <t>SLIMA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1754,7 +1764,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1766,28 +1776,24 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Boyolali 1,2</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6;7</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1801,12 +1807,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Batang (SS Pemalang)</t>
+          <t>Banaran / Sugihrahayu (SS Boyolali)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NBTNG</t>
+          <t>BRNGI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1815,7 +1821,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1829,7 +1835,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Pemalang 1,2</t>
+          <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1862,12 +1868,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bumi Putih (SS Pemalang)</t>
+          <t>New Batang (SS Pemalang)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BNPTH</t>
+          <t>NBTNG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1923,12 +1929,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tanjung Jati (SS Tanjung Jati)</t>
+          <t>Bumi Putih (SS Pemalang)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>BNPTH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1951,7 +1957,7 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
+          <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1984,12 +1990,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kudus (SS Tanjung Jati)</t>
+          <t>Tanjung Jati (SS Tanjung Jati)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KUDUS</t>
+          <t>TJATI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2038,6 +2044,67 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kudus (SS Tanjung Jati)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>KUDUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3367,7 +3434,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUTT Kalisari - Selima (belum energize)</t>
+          <t>SKTT Kalisari - Selima</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3391,7 +3458,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3669,12 +3736,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Tambaklorok jika diperasikan bersamaan Blok 3, Blok 1 dan Blok 2</t>
+          <t>[BELUM_DITETAPKAN] Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Tambaklorok jika diperasikan bersamaan Blok 3, Blok 1 dan Blok 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3844,12 +3911,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Keandalan Subsistem Ungaran 1,2 berkurang apabila hanya PLTGU Tambaklorok Blok 3 beroperasi maksimum</t>
+          <t>[BELUM_DITETAPKAN] Keandalan Subsistem Ungaran 1,2 berkurang apabila hanya PLTGU Tambaklorok Blok 3 beroperasi maksimum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3879,12 +3946,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] SUTT Tambaklorok - Pandeanlamper berbeban &gt;60% apabila PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[BELUM_DITETAPKAN] SUTT Tambaklorok - Pandeanlamper berbeban &gt;60% apabila PLTGU Tambaklorokberoper asi total di atas950 MW</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3914,12 +3981,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] GI Sayung dan SUTT 150 kV Tambaklorok- Sayung 1,2 dengan kondisi kritis karena berada pada tanah dengan kondisi penurunan tanah yang cukup tinggi sekitar ±5 cm perTahun dan dalam kondisi terendam sehingga pondasi dan struktur tower tidak dapat termonitor</t>
+          <t>[BELUM_DITETAPKAN] GI Sayung dan SUTT 150 kV Tambaklorok- Sayung 1,2 dengan kondisi kritis karena berada pada tanah dengan kondisi penurunan tanah yang cukup tinggi sekitar ±5 cm perTahun dan dalam kondisi terendam sehingga pondasi dan struktur tower tidak dapat termonitor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3949,12 +4016,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan Trafo GI Kaliwungu dan GI Randugarut (memasok KTT KEK Kendal) telah berbeban &gt;90%. Daya konsumen KEK Kendal yang tersambung saat ini adalah 181,11 MVA dan pada akhir Tahun 2025 diproyeksikan sebesar 340,25 MVA sehingga kapasitas GI Kaliwungu sudah tidak mencukupi dan berpotensi juga terjadipenurunan tegangan</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan Trafo GI Kaliwungu dan GI Randugarut (memasok KTT KEK Kendal) telah berbeban &gt;90%. Daya konsumen KEK Kendal yang tersambung saat ini adalah 181,11 MVA dan pada akhir Tahun 2025 diproyeksikan sebesar 340,25 MVA sehingga kapasitas GI Kaliwungu sudah tidak mencukupi dan berpotensi juga terjadipenurunan tegangan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3984,12 +4051,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] SUTT Tambaklorok - Krapyak akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KLSRI, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[N-1-1] SUTT Tambaklorok - Krapyak akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KLSRI, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4019,12 +4086,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[N-1] SUTT Tambaklorok - Kalisari akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KRAPK, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[N-1-1] SUTT Tambaklorok - Kalisari akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KRAPK, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
